--- a/data/proc-data/cpi-mospi-processed-inflation.xlsx
+++ b/data/proc-data/cpi-mospi-processed-inflation.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ145"/>
+  <dimension ref="A1:AK145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -613,6 +613,11 @@
           <t>Non Core CPI inflation (food and fuel)</t>
         </is>
       </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>repo_rate</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
@@ -725,6 +730,7 @@
       <c r="AJ2" t="n">
         <v>9.245285192566888</v>
       </c>
+      <c r="AK2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -837,6 +843,7 @@
       <c r="AJ3" t="n">
         <v>7.654503203115182</v>
       </c>
+      <c r="AK3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -949,6 +956,7 @@
       <c r="AJ4" t="n">
         <v>8.301309098661736</v>
       </c>
+      <c r="AK4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -1061,6 +1069,7 @@
       <c r="AJ5" t="n">
         <v>8.74899485897982</v>
       </c>
+      <c r="AK5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -1173,6 +1182,7 @@
       <c r="AJ6" t="n">
         <v>8.360593397423678</v>
       </c>
+      <c r="AK6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -1285,6 +1295,7 @@
       <c r="AJ7" t="n">
         <v>6.869415595385986</v>
       </c>
+      <c r="AK7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -1397,6 +1408,7 @@
       <c r="AJ8" t="n">
         <v>8.290547263681592</v>
       </c>
+      <c r="AK8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -1509,6 +1521,7 @@
       <c r="AJ9" t="n">
         <v>8.111031390310108</v>
       </c>
+      <c r="AK9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -1621,6 +1634,7 @@
       <c r="AJ10" t="n">
         <v>5.880357177346163</v>
       </c>
+      <c r="AK10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -1733,6 +1747,7 @@
       <c r="AJ11" t="n">
         <v>3.826461827425676</v>
       </c>
+      <c r="AK11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -1845,6 +1860,7 @@
       <c r="AJ12" t="n">
         <v>1.409998265429069</v>
       </c>
+      <c r="AK12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -1957,6 +1973,7 @@
       <c r="AJ13" t="n">
         <v>3.890076595536329</v>
       </c>
+      <c r="AK13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -2069,6 +2086,7 @@
       <c r="AJ14" t="n">
         <v>5.849826260730184</v>
       </c>
+      <c r="AK14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
@@ -2181,6 +2199,7 @@
       <c r="AJ15" t="n">
         <v>6.605504161401665</v>
       </c>
+      <c r="AK15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -2293,6 +2312,7 @@
       <c r="AJ16" t="n">
         <v>6.012309764691048</v>
       </c>
+      <c r="AK16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -2405,6 +2425,7 @@
       <c r="AJ17" t="n">
         <v>5.160800485710171</v>
       </c>
+      <c r="AK17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
@@ -2517,6 +2538,7 @@
       <c r="AJ18" t="n">
         <v>4.941241635931659</v>
       </c>
+      <c r="AK18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
@@ -2629,6 +2651,7 @@
       <c r="AJ19" t="n">
         <v>5.520586094446434</v>
       </c>
+      <c r="AK19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
@@ -2741,6 +2764,7 @@
       <c r="AJ20" t="n">
         <v>2.545666715671846</v>
       </c>
+      <c r="AK20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
@@ -2853,6 +2877,7 @@
       <c r="AJ21" t="n">
         <v>2.618897797012476</v>
       </c>
+      <c r="AK21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
@@ -2965,6 +2990,7 @@
       <c r="AJ22" t="n">
         <v>4.050123158475261</v>
       </c>
+      <c r="AK22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
@@ -3077,6 +3103,7 @@
       <c r="AJ23" t="n">
         <v>5.255017901239856</v>
       </c>
+      <c r="AK23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
@@ -3189,6 +3216,7 @@
       <c r="AJ24" t="n">
         <v>5.970676277844955</v>
       </c>
+      <c r="AK24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
@@ -3301,6 +3329,7 @@
       <c r="AJ25" t="n">
         <v>6.284555396532876</v>
       </c>
+      <c r="AK25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
@@ -3413,6 +3442,7 @@
       <c r="AJ26" t="n">
         <v>6.656909326790261</v>
       </c>
+      <c r="AK26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
@@ -3525,6 +3555,7 @@
       <c r="AJ27" t="n">
         <v>5.208664679754138</v>
       </c>
+      <c r="AK27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
@@ -3637,6 +3668,7 @@
       <c r="AJ28" t="n">
         <v>4.992376699716505</v>
       </c>
+      <c r="AK28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
@@ -3749,6 +3781,7 @@
       <c r="AJ29" t="n">
         <v>5.979231751596958</v>
       </c>
+      <c r="AK29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
@@ -3861,6 +3894,7 @@
       <c r="AJ30" t="n">
         <v>6.903372282601206</v>
       </c>
+      <c r="AK30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
@@ -3973,6 +4007,7 @@
       <c r="AJ31" t="n">
         <v>7.189183058729265</v>
       </c>
+      <c r="AK31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
@@ -4085,6 +4120,7 @@
       <c r="AJ32" t="n">
         <v>7.665210606094575</v>
       </c>
+      <c r="AK32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
@@ -4197,6 +4233,7 @@
       <c r="AJ33" t="n">
         <v>5.494362000699371</v>
       </c>
+      <c r="AK33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
@@ -4309,6 +4346,7 @@
       <c r="AJ34" t="n">
         <v>3.853641675312902</v>
       </c>
+      <c r="AK34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
@@ -4421,6 +4459,7 @@
       <c r="AJ35" t="n">
         <v>3.272246299580051</v>
       </c>
+      <c r="AK35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
@@ -4533,6 +4572,7 @@
       <c r="AJ36" t="n">
         <v>2.123398442338753</v>
       </c>
+      <c r="AK36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
@@ -4645,6 +4685,7 @@
       <c r="AJ37" t="n">
         <v>1.662976899597979</v>
       </c>
+      <c r="AK37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
@@ -4757,6 +4798,7 @@
       <c r="AJ38" t="n">
         <v>0.9447838828031241</v>
       </c>
+      <c r="AK38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
@@ -4869,6 +4911,7 @@
       <c r="AJ39" t="n">
         <v>2.24716112447314</v>
       </c>
+      <c r="AK39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
@@ -4981,6 +5024,7 @@
       <c r="AJ40" t="n">
         <v>2.440934542068951</v>
       </c>
+      <c r="AK40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
@@ -5093,6 +5137,7 @@
       <c r="AJ41" t="n">
         <v>1.283007312680895</v>
       </c>
+      <c r="AK41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
@@ -5205,6 +5250,7 @@
       <c r="AJ42" t="n">
         <v>-0.2634425065688339</v>
       </c>
+      <c r="AK42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
@@ -5317,6 +5363,7 @@
       <c r="AJ43" t="n">
         <v>-1.338358551102747</v>
       </c>
+      <c r="AK43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
@@ -5429,6 +5476,7 @@
       <c r="AJ44" t="n">
         <v>0.2511989862157948</v>
       </c>
+      <c r="AK44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
@@ -5541,6 +5589,7 @@
       <c r="AJ45" t="n">
         <v>1.93353762365307</v>
       </c>
+      <c r="AK45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
@@ -5653,6 +5702,7 @@
       <c r="AJ46" t="n">
         <v>1.760622918229893</v>
       </c>
+      <c r="AK46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
@@ -5765,6 +5815,7 @@
       <c r="AJ47" t="n">
         <v>2.432276883599593</v>
       </c>
+      <c r="AK47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
@@ -5877,6 +5928,7 @@
       <c r="AJ48" t="n">
         <v>4.821098572498128</v>
       </c>
+      <c r="AK48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
@@ -5989,6 +6041,7 @@
       <c r="AJ49" t="n">
         <v>5.323971184706822</v>
       </c>
+      <c r="AK49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
@@ -6101,6 +6154,7 @@
       <c r="AJ50" t="n">
         <v>5.08027042415784</v>
       </c>
+      <c r="AK50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
@@ -6213,6 +6267,7 @@
       <c r="AJ51" t="n">
         <v>3.719947323268147</v>
       </c>
+      <c r="AK51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
@@ -6325,6 +6380,7 @@
       <c r="AJ52" t="n">
         <v>3.180100101163585</v>
       </c>
+      <c r="AK52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
@@ -6437,6 +6493,7 @@
       <c r="AJ53" t="n">
         <v>3.102676701116547</v>
       </c>
+      <c r="AK53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
@@ -6549,6 +6606,7 @@
       <c r="AJ54" t="n">
         <v>3.440094524044945</v>
       </c>
+      <c r="AK54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
@@ -6661,6 +6719,7 @@
       <c r="AJ55" t="n">
         <v>3.448617216375127</v>
       </c>
+      <c r="AK55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
@@ -6773,6 +6832,7 @@
       <c r="AJ56" t="n">
         <v>2.116904603976955</v>
       </c>
+      <c r="AK56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
@@ -6885,6 +6945,7 @@
       <c r="AJ57" t="n">
         <v>1.289078984325887</v>
       </c>
+      <c r="AK57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
@@ -6997,6 +7058,7 @@
       <c r="AJ58" t="n">
         <v>1.51224264890879</v>
       </c>
+      <c r="AK58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
@@ -7109,6 +7171,7 @@
       <c r="AJ59" t="n">
         <v>0.3050513544225142</v>
       </c>
+      <c r="AK59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
@@ -7221,6 +7284,7 @@
       <c r="AJ60" t="n">
         <v>-1.384422875709979</v>
       </c>
+      <c r="AK60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
@@ -7331,6 +7395,7 @@
       <c r="AJ61" t="n">
         <v>-1.743062852864707</v>
       </c>
+      <c r="AK61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
@@ -7441,6 +7506,7 @@
       <c r="AJ62" t="n">
         <v>-1.683221856979089</v>
       </c>
+      <c r="AK62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
@@ -7551,6 +7617,7 @@
       <c r="AJ63" t="n">
         <v>-0.4769964052485309</v>
       </c>
+      <c r="AK63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
@@ -7661,6 +7728,7 @@
       <c r="AJ64" t="n">
         <v>0.5628671640767857</v>
       </c>
+      <c r="AK64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
@@ -7771,6 +7839,7 @@
       <c r="AJ65" t="n">
         <v>1.294849868350667</v>
       </c>
+      <c r="AK65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
@@ -7881,6 +7950,7 @@
       <c r="AJ66" t="n">
         <v>1.916349628127634</v>
       </c>
+      <c r="AK66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
@@ -7991,6 +8061,7 @@
       <c r="AJ67" t="n">
         <v>2.246165556026658</v>
       </c>
+      <c r="AK67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
@@ -8101,6 +8172,7 @@
       <c r="AJ68" t="n">
         <v>2.013431548448952</v>
       </c>
+      <c r="AK68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
@@ -8211,6 +8283,7 @@
       <c r="AJ69" t="n">
         <v>2.378749213928377</v>
       </c>
+      <c r="AK69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
@@ -8321,6 +8394,7 @@
       <c r="AJ70" t="n">
         <v>4.145310423698589</v>
       </c>
+      <c r="AK70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
@@ -8433,6 +8507,7 @@
       <c r="AJ71" t="n">
         <v>6.558440919682962</v>
       </c>
+      <c r="AK71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
@@ -8545,6 +8620,7 @@
       <c r="AJ72" t="n">
         <v>8.393280517812363</v>
       </c>
+      <c r="AK72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
@@ -8657,6 +8733,7 @@
       <c r="AJ73" t="n">
         <v>12.36565281598794</v>
       </c>
+      <c r="AK73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
@@ -8769,6 +8846,7 @@
       <c r="AJ74" t="n">
         <v>12.29774060638631</v>
       </c>
+      <c r="AK74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
@@ -8881,6 +8959,7 @@
       <c r="AJ75" t="n">
         <v>10.21720886510336</v>
       </c>
+      <c r="AK75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
@@ -8993,6 +9072,7 @@
       <c r="AJ76" t="n">
         <v>8.467843696690093</v>
       </c>
+      <c r="AK76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
@@ -9105,6 +9185,7 @@
       <c r="AJ77" t="n">
         <v>10.56480830770901</v>
       </c>
+      <c r="AK77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
@@ -9217,6 +9298,7 @@
       <c r="AJ78" t="n">
         <v>8.208893358668568</v>
       </c>
+      <c r="AK78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
@@ -9329,6 +9411,7 @@
       <c r="AJ79" t="n">
         <v>7.649488600652932</v>
       </c>
+      <c r="AK79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
@@ -9441,6 +9524,7 @@
       <c r="AJ80" t="n">
         <v>8.437169948849355</v>
       </c>
+      <c r="AK80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
@@ -9553,6 +9637,7 @@
       <c r="AJ81" t="n">
         <v>8.319115654673027</v>
       </c>
+      <c r="AK81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
@@ -9665,6 +9750,7 @@
       <c r="AJ82" t="n">
         <v>9.703481627388545</v>
       </c>
+      <c r="AK82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
@@ -9777,6 +9863,7 @@
       <c r="AJ83" t="n">
         <v>9.906159809114268</v>
       </c>
+      <c r="AK83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
@@ -9889,6 +9976,7 @@
       <c r="AJ84" t="n">
         <v>8.530670067582612</v>
       </c>
+      <c r="AK84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
@@ -10001,6 +10089,7 @@
       <c r="AJ85" t="n">
         <v>3.35332683690468</v>
       </c>
+      <c r="AK85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
@@ -10113,6 +10202,7 @@
       <c r="AJ86" t="n">
         <v>2.191977355898334</v>
       </c>
+      <c r="AK86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
@@ -10225,6 +10315,7 @@
       <c r="AJ87" t="n">
         <v>3.830698073827943</v>
       </c>
+      <c r="AK87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
@@ -10337,6 +10428,7 @@
       <c r="AJ88" t="n">
         <v>4.81410833257232</v>
       </c>
+      <c r="AK88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
@@ -10449,6 +10541,7 @@
       <c r="AJ89" t="n">
         <v>2.696068408122709</v>
       </c>
+      <c r="AK89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
@@ -10561,6 +10654,7 @@
       <c r="AJ90" t="n">
         <v>5.848254742039294</v>
       </c>
+      <c r="AK90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
@@ -10673,6 +10767,7 @@
       <c r="AJ91" t="n">
         <v>6.054947086510309</v>
       </c>
+      <c r="AK91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
@@ -10785,6 +10880,7 @@
       <c r="AJ92" t="n">
         <v>4.965470748428968</v>
       </c>
+      <c r="AK92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
@@ -10897,6 +10993,7 @@
       <c r="AJ93" t="n">
         <v>4.2762094260826</v>
       </c>
+      <c r="AK93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
@@ -11009,6 +11106,7 @@
       <c r="AJ94" t="n">
         <v>2.191070564424846</v>
       </c>
+      <c r="AK94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
@@ -11121,6 +11219,7 @@
       <c r="AJ95" t="n">
         <v>2.392752075523541</v>
       </c>
+      <c r="AK95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
@@ -11233,6 +11332,7 @@
       <c r="AJ96" t="n">
         <v>3.187440245231721</v>
       </c>
+      <c r="AK96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
@@ -11345,6 +11445,7 @@
       <c r="AJ97" t="n">
         <v>4.881343031284668</v>
       </c>
+      <c r="AK97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
@@ -11457,6 +11558,7 @@
       <c r="AJ98" t="n">
         <v>5.921677801799863</v>
       </c>
+      <c r="AK98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
@@ -11569,6 +11671,7 @@
       <c r="AJ99" t="n">
         <v>6.21874252934369</v>
       </c>
+      <c r="AK99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
@@ -11681,6 +11784,7 @@
       <c r="AJ100" t="n">
         <v>7.657466054489026</v>
       </c>
+      <c r="AK100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
@@ -11793,6 +11897,7 @@
       <c r="AJ101" t="n">
         <v>8.616493185224172</v>
       </c>
+      <c r="AK101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
@@ -11905,6 +12010,7 @@
       <c r="AJ102" t="n">
         <v>8.170939886052754</v>
       </c>
+      <c r="AK102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
@@ -12017,6 +12123,7 @@
       <c r="AJ103" t="n">
         <v>8.056983009923169</v>
       </c>
+      <c r="AK103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
@@ -12129,6 +12236,7 @@
       <c r="AJ104" t="n">
         <v>7.341493634260488</v>
       </c>
+      <c r="AK104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
@@ -12241,6 +12349,7 @@
       <c r="AJ105" t="n">
         <v>8.028581975992255</v>
       </c>
+      <c r="AK105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
@@ -12353,6 +12462,7 @@
       <c r="AJ106" t="n">
         <v>8.836841814284435</v>
       </c>
+      <c r="AK106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
@@ -12465,6 +12575,7 @@
       <c r="AJ107" t="n">
         <v>7.383411631231152</v>
       </c>
+      <c r="AK107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
@@ -12577,6 +12688,7 @@
       <c r="AJ108" t="n">
         <v>5.42259904853557</v>
       </c>
+      <c r="AK108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
@@ -12689,6 +12801,7 @@
       <c r="AJ109" t="n">
         <v>5.047503599619851</v>
       </c>
+      <c r="AK109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
@@ -12801,6 +12914,7 @@
       <c r="AJ110" t="n">
         <v>6.629092681754134</v>
       </c>
+      <c r="AK110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
@@ -12913,6 +13027,7 @@
       <c r="AJ111" t="n">
         <v>6.468643428246046</v>
       </c>
+      <c r="AK111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
@@ -13025,6 +13140,7 @@
       <c r="AJ112" t="n">
         <v>5.31308133210544</v>
       </c>
+      <c r="AK112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
@@ -13137,6 +13253,7 @@
       <c r="AJ113" t="n">
         <v>4.058220548476221</v>
       </c>
+      <c r="AK113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
@@ -13249,6 +13366,7 @@
       <c r="AJ114" t="n">
         <v>3.191166938307033</v>
       </c>
+      <c r="AK114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
@@ -13361,6 +13479,7 @@
       <c r="AJ115" t="n">
         <v>4.463442910353543</v>
       </c>
+      <c r="AK115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
@@ -13473,6 +13592,7 @@
       <c r="AJ116" t="n">
         <v>10.46147531039472</v>
       </c>
+      <c r="AK116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
@@ -13585,6 +13705,7 @@
       <c r="AJ117" t="n">
         <v>9.19296260120146</v>
       </c>
+      <c r="AK117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
@@ -13697,6 +13818,7 @@
       <c r="AJ118" t="n">
         <v>5.735506591727013</v>
       </c>
+      <c r="AK118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
@@ -13809,6 +13931,7 @@
       <c r="AJ119" t="n">
         <v>5.690691863189135</v>
       </c>
+      <c r="AK119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
@@ -13921,6 +14044,7 @@
       <c r="AJ120" t="n">
         <v>7.445172288794044</v>
       </c>
+      <c r="AK120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
@@ -14033,6 +14157,7 @@
       <c r="AJ121" t="n">
         <v>8.115238897461975</v>
       </c>
+      <c r="AK121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
@@ -14145,6 +14270,7 @@
       <c r="AJ122" t="n">
         <v>7.098922732326063</v>
       </c>
+      <c r="AK122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
@@ -14257,6 +14383,7 @@
       <c r="AJ123" t="n">
         <v>7.387964015548976</v>
       </c>
+      <c r="AK123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
@@ -14369,6 +14496,7 @@
       <c r="AJ124" t="n">
         <v>6.924796359676244</v>
       </c>
+      <c r="AK124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
@@ -14481,6 +14609,7 @@
       <c r="AJ125" t="n">
         <v>7.000578542455393</v>
       </c>
+      <c r="AK125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
@@ -14593,6 +14722,7 @@
       <c r="AJ126" t="n">
         <v>7.043127123871562</v>
       </c>
+      <c r="AK126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
@@ -14705,6 +14835,7 @@
       <c r="AJ127" t="n">
         <v>7.663725800564669</v>
       </c>
+      <c r="AK127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="2" t="n">
@@ -14817,6 +14948,7 @@
       <c r="AJ128" t="n">
         <v>4.052266664147308</v>
       </c>
+      <c r="AK128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="2" t="n">
@@ -14929,6 +15061,7 @@
       <c r="AJ129" t="n">
         <v>4.283990732117249</v>
       </c>
+      <c r="AK129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="2" t="n">
@@ -15041,6 +15174,7 @@
       <c r="AJ130" t="n">
         <v>7.921279781270574</v>
       </c>
+      <c r="AK130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" s="2" t="n">
@@ -15153,6 +15287,7 @@
       <c r="AJ131" t="n">
         <v>9.323645174217399</v>
       </c>
+      <c r="AK131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="2" t="n">
@@ -15265,6 +15400,7 @@
       <c r="AJ132" t="n">
         <v>7.712289063634503</v>
       </c>
+      <c r="AK132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" s="2" t="n">
@@ -15377,6 +15513,7 @@
       <c r="AJ133" t="n">
         <v>7.189205928601439</v>
       </c>
+      <c r="AK133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="2" t="n">
@@ -15489,6 +15626,7 @@
       <c r="AJ134" t="n">
         <v>5.038486068775039</v>
       </c>
+      <c r="AK134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" s="2" t="n">
@@ -15601,6 +15739,7 @@
       <c r="AJ135" t="n">
         <v>3.11480691299959</v>
       </c>
+      <c r="AK135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="2" t="n">
@@ -15713,6 +15852,7 @@
       <c r="AJ136" t="n">
         <v>2.533497531973294</v>
       </c>
+      <c r="AK136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" s="2" t="n">
@@ -15825,6 +15965,7 @@
       <c r="AJ137" t="n">
         <v>1.915487573544405</v>
       </c>
+      <c r="AK137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="2" t="n">
@@ -15937,6 +16078,7 @@
       <c r="AJ138" t="n">
         <v>1.2088479211251</v>
       </c>
+      <c r="AK138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" s="2" t="n">
@@ -16049,6 +16191,7 @@
       <c r="AJ139" t="n">
         <v>-0.5906026531181441</v>
       </c>
+      <c r="AK139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" s="2" t="n">
@@ -16161,6 +16304,7 @@
       <c r="AJ140" t="n">
         <v>-1.257424781789318</v>
       </c>
+      <c r="AK140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" s="2" t="n">
@@ -16273,6 +16417,7 @@
       <c r="AJ141" t="n">
         <v>-0.2996615970765504</v>
       </c>
+      <c r="AK141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" s="2" t="n">
@@ -16385,6 +16530,7 @@
       <c r="AJ142" t="n">
         <v>-1.842489620570431</v>
       </c>
+      <c r="AK142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" s="2" t="n">
@@ -16497,6 +16643,7 @@
       <c r="AJ143" t="n">
         <v>-4.243900889208597</v>
       </c>
+      <c r="AK143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" s="2" t="n">
@@ -16609,6 +16756,7 @@
       <c r="AJ144" t="n">
         <v>-3.213556612516399</v>
       </c>
+      <c r="AK144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" s="2" t="n">
@@ -16721,6 +16869,7 @@
       <c r="AJ145" t="n">
         <v>-2.177344420702165</v>
       </c>
+      <c r="AK145" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
